--- a/cidade_alfa_qualidade_ar_ajustado.xlsx
+++ b/cidade_alfa_qualidade_ar_ajustado.xlsx
@@ -1,37 +1,172 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr/>
-  <workbookProtection/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/fc1997508966e77d/Aura_Data/qualidade-ar-cidade-alfa/"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="16" documentId="11_2B59D2BFD3C0D2158571CA734B88083274A7FD86" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5B08F1FF-9355-45A9-B5D6-2B3104891D73}"/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <definedNames/>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="47" uniqueCount="42">
+  <si>
+    <t>id_coleta</t>
+  </si>
+  <si>
+    <t>id_ponto_monitoramento</t>
+  </si>
+  <si>
+    <t>data_coleta</t>
+  </si>
+  <si>
+    <t>regiao</t>
+  </si>
+  <si>
+    <t>bairro</t>
+  </si>
+  <si>
+    <t>tipo_area</t>
+  </si>
+  <si>
+    <t>temperatura_c</t>
+  </si>
+  <si>
+    <t>umidade_%</t>
+  </si>
+  <si>
+    <t>velocidade_vento_kmh</t>
+  </si>
+  <si>
+    <t>chuva_mm</t>
+  </si>
+  <si>
+    <t>pm25_ug_m3</t>
+  </si>
+  <si>
+    <t>pm10_ug_m3</t>
+  </si>
+  <si>
+    <t>co_ppm</t>
+  </si>
+  <si>
+    <t>no2_ppb</t>
+  </si>
+  <si>
+    <t>o3_ppb</t>
+  </si>
+  <si>
+    <t>indice_qualidade_ar</t>
+  </si>
+  <si>
+    <t>qualidade_percebida</t>
+  </si>
+  <si>
+    <t>COL001</t>
+  </si>
+  <si>
+    <t>PNT01</t>
+  </si>
+  <si>
+    <t>Centro</t>
+  </si>
+  <si>
+    <t>Liberdade</t>
+  </si>
+  <si>
+    <t>Urbana</t>
+  </si>
+  <si>
+    <t>Boa</t>
+  </si>
+  <si>
+    <t>COL002</t>
+  </si>
+  <si>
+    <t>PNT02</t>
+  </si>
+  <si>
+    <t>Sul</t>
+  </si>
+  <si>
+    <t>Morumbi</t>
+  </si>
+  <si>
+    <t>Residencial</t>
+  </si>
+  <si>
+    <t>Moderada</t>
+  </si>
+  <si>
+    <t>COL003</t>
+  </si>
+  <si>
+    <t>PNT03</t>
+  </si>
+  <si>
+    <t>Oeste</t>
+  </si>
+  <si>
+    <t>Pinheiros</t>
+  </si>
+  <si>
+    <t>Comercial</t>
+  </si>
+  <si>
+    <t>COL004</t>
+  </si>
+  <si>
+    <t>PNT04</t>
+  </si>
+  <si>
+    <t>COL005</t>
+  </si>
+  <si>
+    <t>PNT05</t>
+  </si>
+  <si>
+    <t>Norte</t>
+  </si>
+  <si>
+    <t>Santana</t>
+  </si>
+  <si>
+    <t>Mista</t>
+  </si>
+  <si>
+    <t>Ruim</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
-    <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
-    <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="1">
+    <numFmt numFmtId="165" formatCode="yyyy\-mm\-dd\ hh:mm:ss"/>
   </numFmts>
-  <fonts count="1">
+  <fonts count="1" x14ac:knownFonts="1">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <color theme="1"/>
-      <sz val="11"/>
       <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill/>
+      <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -50,81 +185,22 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="2">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008000"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00808000"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="00C0C0C0"/>
-      <rgbColor rgb="00808080"/>
-      <rgbColor rgb="009999FF"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00FFFFCC"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00660066"/>
-      <rgbColor rgb="00FF8080"/>
-      <rgbColor rgb="000066CC"/>
-      <rgbColor rgb="00CCCCFF"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="0000CCFF"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00CCFFCC"/>
-      <rgbColor rgb="00FFFF99"/>
-      <rgbColor rgb="0099CCFF"/>
-      <rgbColor rgb="00FF99CC"/>
-      <rgbColor rgb="00CC99FF"/>
-      <rgbColor rgb="00FFCC99"/>
-      <rgbColor rgb="003366FF"/>
-      <rgbColor rgb="0033CCCC"/>
-      <rgbColor rgb="0099CC00"/>
-      <rgbColor rgb="00FFCC00"/>
-      <rgbColor rgb="00FF9900"/>
-      <rgbColor rgb="00FF6600"/>
-      <rgbColor rgb="00666699"/>
-      <rgbColor rgb="00969696"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
-    </indexedColors>
-  </colors>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -412,424 +488,343 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:Q6"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="8.5546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="22.5546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="18.109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="6.5546875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="9" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="10.109375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="13.21875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="10.44140625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="20.109375" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="9.88671875" bestFit="1" customWidth="1"/>
+    <col min="11" max="12" width="12" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="8.109375" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="7.109375" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="17.5546875" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="18.109375" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>id_coleta</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>id_ponto_monitoramento</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>data_coleta</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>regiao</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>bairro</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>tipo_area</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>temperatura_c</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>umidade_%</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>velocidade_vento_kmh</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>chuva_mm</t>
-        </is>
-      </c>
-      <c r="K1" t="inlineStr">
-        <is>
-          <t>pm25_ug_m3</t>
-        </is>
-      </c>
-      <c r="L1" t="inlineStr">
-        <is>
-          <t>pm10_ug_m3</t>
-        </is>
-      </c>
-      <c r="M1" t="inlineStr">
-        <is>
-          <t>co_ppm</t>
-        </is>
-      </c>
-      <c r="N1" t="inlineStr">
-        <is>
-          <t>no2_ppb</t>
-        </is>
-      </c>
-      <c r="O1" t="inlineStr">
-        <is>
-          <t>o3_ppb</t>
-        </is>
-      </c>
-      <c r="P1" t="inlineStr">
-        <is>
-          <t>indice_qualidade_ar</t>
-        </is>
-      </c>
-      <c r="Q1" t="inlineStr">
-        <is>
-          <t>qualidade_percebida</t>
-        </is>
+    <row r="1" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" t="s">
+        <v>13</v>
+      </c>
+      <c r="O1" t="s">
+        <v>14</v>
+      </c>
+      <c r="P1" t="s">
+        <v>15</v>
+      </c>
+      <c r="Q1" t="s">
+        <v>16</v>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>COL001</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>PNT01</t>
-        </is>
-      </c>
-      <c r="C2" s="1" t="n">
-        <v>46266.33333333334</v>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>Centro</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>Liberdade</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>Urbana</t>
-        </is>
-      </c>
-      <c r="G2" t="n">
+    <row r="2" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>17</v>
+      </c>
+      <c r="B2" t="s">
+        <v>18</v>
+      </c>
+      <c r="C2" s="1">
+        <v>46266.333333333343</v>
+      </c>
+      <c r="D2" t="s">
+        <v>19</v>
+      </c>
+      <c r="E2" t="s">
+        <v>20</v>
+      </c>
+      <c r="F2" t="s">
+        <v>21</v>
+      </c>
+      <c r="G2">
         <v>22.5</v>
       </c>
-      <c r="H2" t="n">
+      <c r="H2">
         <v>65</v>
       </c>
-      <c r="I2" t="n">
+      <c r="I2">
         <v>12</v>
       </c>
-      <c r="J2" t="n">
+      <c r="J2">
         <v>0</v>
       </c>
-      <c r="K2" t="n">
+      <c r="K2">
         <v>18.5</v>
       </c>
-      <c r="L2" t="n">
+      <c r="L2">
         <v>42</v>
       </c>
-      <c r="M2" t="n">
+      <c r="M2">
         <v>0.8</v>
       </c>
-      <c r="N2" t="n">
+      <c r="N2">
         <v>25.4</v>
       </c>
-      <c r="O2" t="n">
-        <v>40.2</v>
-      </c>
-      <c r="P2" t="n">
+      <c r="O2">
+        <v>40.200000000000003</v>
+      </c>
+      <c r="P2">
         <v>45</v>
       </c>
-      <c r="Q2" t="inlineStr">
-        <is>
-          <t>Boa</t>
-        </is>
+      <c r="Q2" t="s">
+        <v>22</v>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>COL002</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>PNT02</t>
-        </is>
-      </c>
-      <c r="C3" s="1" t="n">
+    <row r="3" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>23</v>
+      </c>
+      <c r="B3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C3" s="1">
         <v>46266.375</v>
       </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>Sul</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>Morumbi</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>Residencial</t>
-        </is>
-      </c>
-      <c r="G3" t="n">
+      <c r="D3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E3" t="s">
+        <v>26</v>
+      </c>
+      <c r="F3" t="s">
+        <v>27</v>
+      </c>
+      <c r="G3">
         <v>24</v>
       </c>
-      <c r="H3" t="n">
+      <c r="H3">
         <v>58</v>
       </c>
-      <c r="I3" t="n">
+      <c r="I3">
         <v>8.5</v>
       </c>
-      <c r="J3" t="n">
+      <c r="J3">
         <v>0</v>
       </c>
-      <c r="K3" t="n">
+      <c r="K3">
         <v>25</v>
       </c>
-      <c r="L3" t="n">
+      <c r="L3">
         <v>55.3</v>
       </c>
-      <c r="M3" t="n">
+      <c r="M3">
         <v>1.2</v>
       </c>
-      <c r="N3" t="n">
+      <c r="N3">
         <v>32.1</v>
       </c>
-      <c r="O3" t="n">
+      <c r="O3">
         <v>48.6</v>
       </c>
-      <c r="P3" t="n">
+      <c r="P3">
         <v>62</v>
       </c>
-      <c r="Q3" t="inlineStr">
-        <is>
-          <t>Moderada</t>
-        </is>
+      <c r="Q3" t="s">
+        <v>28</v>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>COL003</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>PNT03</t>
-        </is>
-      </c>
-      <c r="C4" s="1" t="n">
-        <v>46266.41666666666</v>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>Oeste</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>Pinheiros</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>Comercial</t>
-        </is>
-      </c>
-      <c r="G4" t="n">
+    <row r="4" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>29</v>
+      </c>
+      <c r="B4" t="s">
+        <v>30</v>
+      </c>
+      <c r="C4" s="1">
+        <v>46266.416666666657</v>
+      </c>
+      <c r="D4" t="s">
+        <v>31</v>
+      </c>
+      <c r="E4" t="s">
+        <v>32</v>
+      </c>
+      <c r="F4" t="s">
+        <v>33</v>
+      </c>
+      <c r="G4">
         <v>26.1</v>
       </c>
-      <c r="H4" t="n">
+      <c r="H4">
         <v>52</v>
       </c>
-      <c r="I4" t="n">
+      <c r="I4">
         <v>15.2</v>
       </c>
-      <c r="J4" t="n">
+      <c r="J4">
         <v>1.2</v>
       </c>
-      <c r="K4" t="n">
+      <c r="K4">
         <v>12.1</v>
       </c>
-      <c r="L4" t="n">
+      <c r="L4">
         <v>30</v>
       </c>
-      <c r="M4" t="n">
+      <c r="M4">
         <v>0.5</v>
       </c>
-      <c r="N4" t="n">
+      <c r="N4">
         <v>18</v>
       </c>
-      <c r="O4" t="n">
+      <c r="O4">
         <v>35.1</v>
       </c>
-      <c r="P4" t="n">
+      <c r="P4">
         <v>30</v>
       </c>
-      <c r="Q4" t="inlineStr">
-        <is>
-          <t>Boa</t>
-        </is>
+      <c r="Q4" t="s">
+        <v>22</v>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>COL004</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>PNT04</t>
-        </is>
-      </c>
-      <c r="C5" s="1" t="n">
-        <v>46266.41666666666</v>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>Oeste</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>Pinheiros</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>Comercial</t>
-        </is>
-      </c>
-      <c r="G5" t="n">
+    <row r="5" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>34</v>
+      </c>
+      <c r="B5" t="s">
+        <v>35</v>
+      </c>
+      <c r="C5" s="1">
+        <v>46266.416666666657</v>
+      </c>
+      <c r="D5" t="s">
+        <v>31</v>
+      </c>
+      <c r="E5" t="s">
+        <v>32</v>
+      </c>
+      <c r="F5" t="s">
+        <v>33</v>
+      </c>
+      <c r="G5">
         <v>26.1</v>
       </c>
-      <c r="H5" t="n">
+      <c r="H5">
         <v>52</v>
       </c>
-      <c r="I5" t="n">
+      <c r="I5">
         <v>15.2</v>
       </c>
-      <c r="J5" t="n">
+      <c r="J5">
         <v>1.2</v>
       </c>
-      <c r="K5" t="n">
+      <c r="K5">
         <v>12.1</v>
       </c>
-      <c r="L5" t="n">
+      <c r="L5">
         <v>30</v>
       </c>
-      <c r="M5" t="n">
+      <c r="M5">
         <v>0.5</v>
       </c>
-      <c r="N5" t="n">
+      <c r="N5">
         <v>18</v>
       </c>
-      <c r="O5" t="n">
+      <c r="O5">
         <v>35.1</v>
       </c>
-      <c r="P5" t="n">
+      <c r="P5">
         <v>30</v>
       </c>
-      <c r="Q5" t="inlineStr">
-        <is>
-          <t>Boa</t>
-        </is>
+      <c r="Q5" t="s">
+        <v>22</v>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>COL005</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>PNT05</t>
-        </is>
-      </c>
-      <c r="C6" s="1" t="n">
-        <v>46266.45833333334</v>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>Norte</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>Santana</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>Mista</t>
-        </is>
-      </c>
-      <c r="G6" t="n">
+    <row r="6" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>36</v>
+      </c>
+      <c r="B6" t="s">
+        <v>37</v>
+      </c>
+      <c r="C6" s="1">
+        <v>46266.458333333343</v>
+      </c>
+      <c r="D6" t="s">
+        <v>38</v>
+      </c>
+      <c r="E6" t="s">
+        <v>39</v>
+      </c>
+      <c r="F6" t="s">
+        <v>40</v>
+      </c>
+      <c r="G6">
         <v>27.8</v>
       </c>
-      <c r="H6" t="n">
+      <c r="H6">
         <v>48</v>
       </c>
-      <c r="I6" t="n">
+      <c r="I6">
         <v>6</v>
       </c>
-      <c r="J6" t="n">
+      <c r="J6">
         <v>0</v>
       </c>
-      <c r="K6" t="n">
+      <c r="K6">
         <v>38.4</v>
       </c>
-      <c r="L6" t="n">
-        <v>72.09999999999999</v>
-      </c>
-      <c r="M6" t="n">
+      <c r="L6">
+        <v>72.099999999999994</v>
+      </c>
+      <c r="M6">
         <v>1.7</v>
       </c>
-      <c r="N6" t="n">
+      <c r="N6">
         <v>45</v>
       </c>
-      <c r="O6" t="n">
+      <c r="O6">
         <v>60.2</v>
       </c>
-      <c r="P6" t="n">
+      <c r="P6">
         <v>85</v>
       </c>
-      <c r="Q6" t="inlineStr">
-        <is>
-          <t>Ruim</t>
-        </is>
+      <c r="Q6" t="s">
+        <v>41</v>
       </c>
     </row>
   </sheetData>
